--- a/ig/main/CodeSystem-tre-r395-engagement.xlsx
+++ b/ig/main/CodeSystem-tre-r395-engagement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="154">
   <si>
     <t>Property</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>ARR</t>
+  </si>
+  <si>
+    <t>Arrêtés (sans autre indication)</t>
   </si>
   <si>
     <t>ASD</t>
@@ -1019,7 +1022,7 @@
         <v>84</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -1028,10 +1031,10 @@
         <v>70</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -1040,10 +1043,10 @@
         <v>70</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -1052,10 +1055,10 @@
         <v>70</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -1064,10 +1067,10 @@
         <v>70</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -1076,10 +1079,10 @@
         <v>70</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -1088,10 +1091,10 @@
         <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -1100,10 +1103,10 @@
         <v>70</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -1112,13 +1115,13 @@
         <v>70</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -1126,10 +1129,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -1138,10 +1141,10 @@
         <v>70</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -1150,10 +1153,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -1162,10 +1165,10 @@
         <v>70</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -1174,10 +1177,10 @@
         <v>70</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -1186,10 +1189,10 @@
         <v>70</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -1198,13 +1201,13 @@
         <v>70</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24">
@@ -1212,10 +1215,10 @@
         <v>70</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -1224,10 +1227,10 @@
         <v>70</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -1236,10 +1239,10 @@
         <v>70</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -1248,10 +1251,10 @@
         <v>70</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -1260,10 +1263,10 @@
         <v>70</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -1272,10 +1275,10 @@
         <v>70</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -1284,13 +1287,13 @@
         <v>70</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31">
@@ -1298,10 +1301,10 @@
         <v>70</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -1310,10 +1313,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -1322,10 +1325,10 @@
         <v>70</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -1334,10 +1337,10 @@
         <v>70</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" s="2"/>
     </row>
@@ -1346,13 +1349,13 @@
         <v>70</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36">
@@ -1360,10 +1363,10 @@
         <v>70</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -1372,10 +1375,10 @@
         <v>70</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -1384,10 +1387,10 @@
         <v>70</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -1396,10 +1399,10 @@
         <v>70</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -1408,10 +1411,10 @@
         <v>70</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D40" s="2"/>
     </row>
